--- a/Input/Noor_Takaful/rateSheet.xlsx
+++ b/Input/Noor_Takaful/rateSheet.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="19">
   <si>
     <t xml:space="preserve">planName</t>
   </si>
@@ -49,6 +49,9 @@
     <t xml:space="preserve">frequency</t>
   </si>
   <si>
+    <t xml:space="preserve">currency</t>
+  </si>
+  <si>
     <t xml:space="preserve">Plan 1</t>
   </si>
   <si>
@@ -65,6 +68,9 @@
   </si>
   <si>
     <t xml:space="preserve">Annually</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USD</t>
   </si>
   <si>
     <t xml:space="preserve">female</t>
@@ -86,6 +92,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -106,12 +113,14 @@
       <sz val="9"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -190,7 +199,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="11.52"/>
@@ -226,16 +235,19 @@
       <c r="I1" s="0" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="0" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="0" t="n">
         <v>0</v>
@@ -247,24 +259,27 @@
         <v>470</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J2" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="0" t="n">
         <v>0</v>
@@ -276,24 +291,27 @@
         <v>470</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J3" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="0" t="n">
         <v>46</v>
@@ -305,24 +323,27 @@
         <v>815</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J4" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" s="0" t="n">
         <v>46</v>
@@ -334,24 +355,27 @@
         <v>815</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J5" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" s="0" t="n">
         <v>66</v>
@@ -363,24 +387,27 @@
         <v>3000</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J6" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" s="0" t="n">
         <v>66</v>
@@ -392,24 +419,27 @@
         <v>3000</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J7" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" s="0" t="n">
         <v>0</v>
@@ -421,24 +451,27 @@
         <v>585</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J8" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" s="0" t="n">
         <v>0</v>
@@ -450,24 +483,27 @@
         <v>585</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J9" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" s="0" t="n">
         <v>46</v>
@@ -479,24 +515,27 @@
         <v>1030</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J10" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" s="0" t="n">
         <v>46</v>
@@ -508,24 +547,27 @@
         <v>1030</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J11" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" s="0" t="n">
         <v>66</v>
@@ -537,24 +579,27 @@
         <v>3999</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J12" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" s="0" t="n">
         <v>66</v>
@@ -566,13 +611,16 @@
         <v>3999</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J13" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
